--- a/dataset_t6_grouped/results2/G5/G5_T2372_W0066F0002T0006Z000C1N32_analysis.xlsx
+++ b/dataset_t6_grouped/results2/G5/G5_T2372_W0066F0002T0006Z000C1N32_analysis.xlsx
@@ -480,16 +480,16 @@
         <v>1</v>
       </c>
       <c r="C2" t="n">
-        <v>31.69710897376658</v>
+        <v>5.15078020823707</v>
       </c>
       <c r="D2" t="n">
-        <v>31.58288675389828</v>
+        <v>5.132219097508471</v>
       </c>
       <c r="E2" t="n">
-        <v>9.163303450068817</v>
+        <v>1.489036810636183</v>
       </c>
       <c r="F2" t="n">
-        <v>9.075375207855767</v>
+        <v>1.474748471276562</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -512,16 +512,16 @@
         <v>2</v>
       </c>
       <c r="C3" t="n">
-        <v>25.24251718364658</v>
+        <v>4.10190904234257</v>
       </c>
       <c r="D3" t="n">
-        <v>25.02842540476361</v>
+        <v>4.067119128274087</v>
       </c>
       <c r="E3" t="n">
-        <v>9.163303450068817</v>
+        <v>1.489036810636183</v>
       </c>
       <c r="F3" t="n">
-        <v>9.075375207855767</v>
+        <v>1.474748471276562</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
@@ -544,16 +544,16 @@
         <v>3</v>
       </c>
       <c r="C4" t="n">
-        <v>3.038078298875535</v>
+        <v>0.4936877235672745</v>
       </c>
       <c r="D4" t="n">
-        <v>3.263075274257652</v>
+        <v>0.5302497320668685</v>
       </c>
       <c r="E4" t="n">
-        <v>9.163303450068817</v>
+        <v>1.489036810636183</v>
       </c>
       <c r="F4" t="n">
-        <v>9.075375207855767</v>
+        <v>1.474748471276562</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
@@ -576,16 +576,16 @@
         <v>4</v>
       </c>
       <c r="C5" t="n">
-        <v>19.65254194413499</v>
+        <v>3.193538065921936</v>
       </c>
       <c r="D5" t="n">
-        <v>19.57217625921357</v>
+        <v>3.180478642122205</v>
       </c>
       <c r="E5" t="n">
-        <v>9.163303450068817</v>
+        <v>1.489036810636183</v>
       </c>
       <c r="F5" t="n">
-        <v>9.075375207855767</v>
+        <v>1.474748471276562</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
@@ -608,16 +608,16 @@
         <v>5</v>
       </c>
       <c r="C6" t="n">
-        <v>20.80475358833981</v>
+        <v>3.380772458105219</v>
       </c>
       <c r="D6" t="n">
-        <v>20.86892474505741</v>
+        <v>3.391200271071829</v>
       </c>
       <c r="E6" t="n">
-        <v>9.163303450068817</v>
+        <v>1.489036810636183</v>
       </c>
       <c r="F6" t="n">
-        <v>9.075375207855767</v>
+        <v>1.474748471276562</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
@@ -640,16 +640,16 @@
         <v>6</v>
       </c>
       <c r="C7" t="n">
-        <v>22.13687600495172</v>
+        <v>3.597242350804654</v>
       </c>
       <c r="D7" t="n">
-        <v>22.24067253367818</v>
+        <v>3.614109286722704</v>
       </c>
       <c r="E7" t="n">
-        <v>9.163303450068817</v>
+        <v>1.489036810636183</v>
       </c>
       <c r="F7" t="n">
-        <v>9.075375207855767</v>
+        <v>1.474748471276562</v>
       </c>
       <c r="G7" t="inlineStr">
         <is>
@@ -672,16 +672,16 @@
         <v>7</v>
       </c>
       <c r="C8" t="n">
-        <v>32.81562341377303</v>
+        <v>5.332538804738117</v>
       </c>
       <c r="D8" t="n">
-        <v>32.84013640536858</v>
+        <v>5.336522165872394</v>
       </c>
       <c r="E8" t="n">
-        <v>9.163303450068817</v>
+        <v>1.489036810636183</v>
       </c>
       <c r="F8" t="n">
-        <v>9.075375207855767</v>
+        <v>1.474748471276562</v>
       </c>
       <c r="G8" t="inlineStr">
         <is>
